--- a/ig/nr-INS-Patient/StructureDefinition-fr-core-slot.xlsx
+++ b/ig/nr-INS-Patient/StructureDefinition-fr-core-slot.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="264">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T12:02:48+00:00</t>
+    <t>2023-10-16T13:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -201,13 +201,203 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Slot.implicitRules</t>
+    <t>Slot.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Slot.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Slot.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Slot.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Slot.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Slot.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Slot.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>Slot.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Slot.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Slot.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -300,38 +490,10 @@
     <t>Slot.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Slot.modifierExtension</t>
@@ -372,26 +534,7 @@
     <t>Slot.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Slot.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Slot.identifier.use</t>
@@ -440,9 +583,6 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
@@ -562,9 +702,6 @@
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/service-category</t>
   </si>
   <si>
@@ -648,10 +785,6 @@
   </si>
   <si>
     <t>Slot.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
   </si>
   <si>
     <t>Date/Time that the slot is to begin</t>
@@ -1005,11 +1138,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM28"/>
+  <dimension ref="A1:AM37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="22.921875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.71484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="22.921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.83203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="6" max="6" width="2.2109375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="2.2109375" customWidth="true" bestFit="true"/>
@@ -1030,17 +1164,16 @@
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="57.77734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="10.26171875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="12.34765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="33.88671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="2.2109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" hidden="true" width="8.0" customWidth="false"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="143.74609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="128.8359375" customWidth="true" bestFit="true"/>
@@ -1398,10 +1531,10 @@
         <v>35</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>61</v>
@@ -1412,9 +1545,7 @@
       <c r="M4" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="N4" t="s" s="2">
-        <v>64</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>35</v>
@@ -1463,7 +1594,7 @@
         <v>35</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>36</v>
@@ -1472,10 +1603,10 @@
         <v>45</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>42</v>
@@ -1489,21 +1620,21 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>35</v>
@@ -1550,28 +1681,28 @@
         <v>35</v>
       </c>
       <c r="X5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB5" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Y5" t="s" s="2">
+      <c r="AC5" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="Z5" t="s" s="2">
+      <c r="AD5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE5" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>35</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>74</v>
@@ -1580,16 +1711,16 @@
         <v>36</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>35</v>
@@ -1600,14 +1731,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -1623,19 +1754,19 @@
         <v>35</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>79</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1685,7 +1816,7 @@
         <v>35</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>36</v>
@@ -1700,7 +1831,7 @@
         <v>58</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>35</v>
@@ -1711,21 +1842,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>35</v>
@@ -1734,19 +1865,19 @@
         <v>35</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1796,22 +1927,22 @@
         <v>35</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>35</v>
@@ -1822,21 +1953,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>35</v>
@@ -1845,19 +1976,19 @@
         <v>35</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1895,34 +2026,34 @@
         <v>35</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>35</v>
@@ -1933,14 +2064,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1953,26 +2084,24 @@
         <v>35</v>
       </c>
       <c r="I9" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J9" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="J9" t="s" s="2">
-        <v>35</v>
-      </c>
       <c r="K9" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>35</v>
       </c>
@@ -2008,19 +2137,19 @@
         <v>35</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>36</v>
@@ -2032,10 +2161,10 @@
         <v>57</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>35</v>
@@ -2046,12 +2175,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>35</v>
       </c>
@@ -2060,7 +2191,7 @@
         <v>36</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>35</v>
@@ -2072,15 +2203,17 @@
         <v>46</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>35</v>
@@ -2090,7 +2223,7 @@
         <v>35</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>35</v>
@@ -2129,7 +2262,7 @@
         <v>35</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>36</v>
@@ -2144,21 +2277,21 @@
         <v>58</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>111</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2169,7 +2302,7 @@
         <v>36</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>35</v>
@@ -2178,18 +2311,20 @@
         <v>35</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>35</v>
@@ -2214,13 +2349,13 @@
         <v>35</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>35</v>
@@ -2238,22 +2373,22 @@
         <v>35</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>35</v>
@@ -2264,14 +2399,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2287,19 +2422,19 @@
         <v>35</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2325,31 +2460,31 @@
         <v>35</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>36</v>
@@ -2361,10 +2496,10 @@
         <v>57</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>35</v>
@@ -2375,10 +2510,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2401,20 +2536,18 @@
         <v>46</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="O13" t="s" s="2">
         <v>124</v>
       </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>35</v>
       </c>
@@ -2438,29 +2571,31 @@
         <v>35</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="Y13" s="2"/>
-      <c r="Z13" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>36</v>
@@ -2475,7 +2610,7 @@
         <v>58</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>35</v>
@@ -2486,10 +2621,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2509,23 +2644,21 @@
         <v>35</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>134</v>
-      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>35</v>
       </c>
@@ -2549,13 +2682,13 @@
         <v>35</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>35</v>
@@ -2573,7 +2706,7 @@
         <v>35</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>36</v>
@@ -2588,7 +2721,7 @@
         <v>58</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>35</v>
@@ -2599,14 +2732,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2622,23 +2755,21 @@
         <v>35</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>35</v>
       </c>
@@ -2650,7 +2781,7 @@
         <v>35</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>144</v>
+        <v>35</v>
       </c>
       <c r="U15" t="s" s="2">
         <v>35</v>
@@ -2686,7 +2817,7 @@
         <v>35</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>36</v>
@@ -2701,7 +2832,7 @@
         <v>58</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>35</v>
@@ -2712,21 +2843,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>35</v>
@@ -2735,19 +2866,19 @@
         <v>35</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2761,7 +2892,7 @@
         <v>35</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>35</v>
@@ -2797,22 +2928,22 @@
         <v>35</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>35</v>
@@ -2823,21 +2954,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>35</v>
@@ -2846,19 +2977,19 @@
         <v>35</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2896,34 +3027,34 @@
         <v>35</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>161</v>
+        <v>59</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>35</v>
@@ -2934,44 +3065,46 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>35</v>
       </c>
@@ -3007,34 +3140,34 @@
         <v>35</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>168</v>
+        <v>75</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>35</v>
@@ -3045,10 +3178,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3059,7 +3192,7 @@
         <v>36</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>35</v>
@@ -3071,17 +3204,15 @@
         <v>46</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>35</v>
@@ -3106,11 +3237,13 @@
         <v>35</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>175</v>
+        <v>35</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>35</v>
@@ -3128,7 +3261,7 @@
         <v>35</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>36</v>
@@ -3143,21 +3276,21 @@
         <v>58</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>177</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3168,7 +3301,7 @@
         <v>36</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>35</v>
@@ -3177,20 +3310,18 @@
         <v>35</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>179</v>
+        <v>62</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>35</v>
@@ -3215,11 +3346,13 @@
         <v>35</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>181</v>
+        <v>35</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>35</v>
@@ -3237,40 +3370,40 @@
         <v>35</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>176</v>
+        <v>42</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>177</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3286,19 +3419,19 @@
         <v>35</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>183</v>
+        <v>68</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3324,29 +3457,31 @@
         <v>35</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>185</v>
+        <v>35</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>182</v>
+        <v>74</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>36</v>
@@ -3358,24 +3493,24 @@
         <v>57</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>176</v>
+        <v>59</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>177</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3392,24 +3527,26 @@
         <v>35</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>46</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>35</v>
       </c>
@@ -3433,11 +3570,11 @@
         <v>35</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>35</v>
@@ -3455,7 +3592,7 @@
         <v>35</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -3470,21 +3607,21 @@
         <v>58</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>177</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3492,7 +3629,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>45</v>
@@ -3507,18 +3644,20 @@
         <v>46</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>35</v>
       </c>
@@ -3542,13 +3681,13 @@
         <v>35</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>35</v>
+        <v>181</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>35</v>
@@ -3566,10 +3705,10 @@
         <v>35</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>45</v>
@@ -3578,10 +3717,10 @@
         <v>57</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>35</v>
@@ -3592,10 +3731,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3603,7 +3742,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>45</v>
@@ -3618,18 +3757,20 @@
         <v>46</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>35</v>
       </c>
@@ -3641,7 +3782,7 @@
         <v>35</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>35</v>
@@ -3653,11 +3794,13 @@
         <v>35</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>35</v>
@@ -3675,10 +3818,10 @@
         <v>35</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>45</v>
@@ -3690,10 +3833,10 @@
         <v>58</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>42</v>
+        <v>191</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>35</v>
@@ -3701,10 +3844,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3712,7 +3855,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>45</v>
@@ -3727,16 +3870,16 @@
         <v>46</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>203</v>
+        <v>61</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3750,7 +3893,7 @@
         <v>35</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>35</v>
+        <v>196</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>35</v>
@@ -3786,10 +3929,10 @@
         <v>35</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>45</v>
@@ -3801,21 +3944,21 @@
         <v>58</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>42</v>
+        <v>198</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>207</v>
+        <v>35</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>208</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3823,7 +3966,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>45</v>
@@ -3838,16 +3981,16 @@
         <v>46</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3897,10 +4040,10 @@
         <v>35</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>45</v>
@@ -3909,24 +4052,24 @@
         <v>57</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>58</v>
+        <v>205</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>208</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3946,25 +4089,25 @@
         <v>35</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="Q27" t="s" s="2">
-        <v>217</v>
-      </c>
+      <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
         <v>35</v>
       </c>
@@ -4008,7 +4151,7 @@
         <v>35</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
@@ -4020,10 +4163,10 @@
         <v>57</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>42</v>
+        <v>214</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>35</v>
@@ -4034,10 +4177,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4057,19 +4200,19 @@
         <v>35</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4095,13 +4238,11 @@
         <v>35</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>35</v>
+        <v>219</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>35</v>
@@ -4119,13 +4260,13 @@
         <v>35</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>57</v>
@@ -4134,12 +4275,1003 @@
         <v>58</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="Y29" s="2"/>
+      <c r="Z29" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Y30" s="2"/>
+      <c r="Z30" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="Y31" s="2"/>
+      <c r="Z31" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Y33" s="2"/>
+      <c r="Z33" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK33" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AL33" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q36" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="R36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>35</v>
       </c>
     </row>
